--- a/data_cover.xlsx
+++ b/data_cover.xlsx
@@ -494,10 +494,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -514,10 +512,8 @@
           <t>2016 – 2021</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="E2" t="n">
+        <v>10</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -551,10 +547,8 @@
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -571,10 +565,8 @@
           <t>2022-ON</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="E3" t="n">
+        <v>10</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -608,10 +600,8 @@
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A4" t="n">
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -628,10 +618,8 @@
           <t>2021-ON</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
+      <c r="E4" t="n">
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -665,10 +653,8 @@
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A5" t="n">
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -685,10 +671,8 @@
           <t>2006-2013</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
+      <c r="E5" t="n">
+        <v>5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -722,10 +706,8 @@
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="A6" t="n">
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -742,10 +724,8 @@
           <t>2014-2017</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
+      <c r="E6" t="n">
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -779,10 +759,8 @@
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A7" t="n">
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -799,10 +777,8 @@
           <t>2023-ON</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
+      <c r="E7" t="n">
+        <v>9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -836,10 +812,8 @@
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -856,10 +830,8 @@
           <t xml:space="preserve">2017 – 2020 </t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+      <c r="E8" t="n">
+        <v>8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -893,10 +865,8 @@
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A9" t="n">
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -913,10 +883,8 @@
           <t>2021 – 2023</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+      <c r="E9" t="n">
+        <v>8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -950,10 +918,8 @@
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A10" t="n">
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -970,10 +936,8 @@
           <t>1998-2007</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="E10" t="n">
+        <v>14</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1007,10 +971,8 @@
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A11" t="n">
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1027,10 +989,8 @@
           <t>2019-2024</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="E11" t="n">
+        <v>13</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1064,10 +1024,8 @@
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A12" t="n">
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1084,10 +1042,8 @@
           <t>2012-2018</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="E12" t="n">
+        <v>6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1121,10 +1077,8 @@
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A13" t="n">
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1141,10 +1095,8 @@
           <t>2022-ON</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="E13" t="n">
+        <v>10</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1178,10 +1130,8 @@
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="A14" t="n">
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1198,10 +1148,8 @@
           <t>2022-ON</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="E14" t="n">
+        <v>10</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1231,10 +1179,8 @@
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="A15" t="n">
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1251,10 +1197,8 @@
           <t>2001 – 2007</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="E15" t="n">
+        <v>6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1288,10 +1232,8 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="A16" t="n">
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1308,10 +1250,8 @@
           <t>2008 – 2013</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="E16" t="n">
+        <v>6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1345,10 +1285,8 @@
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="A17" t="n">
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1365,10 +1303,8 @@
           <t>2014 – 2019</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="E17" t="n">
+        <v>6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1402,10 +1338,8 @@
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="A18" t="n">
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1422,10 +1356,8 @@
           <t>2019-ON</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="E18" t="n">
+        <v>6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1459,10 +1391,8 @@
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="A19" t="n">
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1479,10 +1409,8 @@
           <t>1950 – 1967</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="E19" t="n">
+        <v>16</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1516,10 +1444,8 @@
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="A20" t="n">
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1536,10 +1462,8 @@
           <t>1967 – 1979</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="E20" t="n">
+        <v>16</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1573,10 +1497,8 @@
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="A21" t="n">
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1593,10 +1515,8 @@
           <t>2002–2014</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="E21" t="n">
+        <v>14</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1630,10 +1550,8 @@
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="A22" t="n">
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1650,10 +1568,8 @@
           <t>2015-ON</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="E22" t="n">
+        <v>14</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1687,10 +1603,8 @@
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="A23" t="n">
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1707,10 +1621,8 @@
           <t>2007-2021</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="E23" t="n">
+        <v>11</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1744,10 +1656,8 @@
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="A24" t="n">
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1764,10 +1674,8 @@
           <t>2022-ON</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="E24" t="n">
+        <v>14</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1801,10 +1709,8 @@
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="A25" t="n">
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1821,10 +1727,8 @@
           <t>2018-ON</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="E25" t="n">
+        <v>13</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1862,10 +1766,8 @@
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="A26" t="n">
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1882,10 +1784,8 @@
           <t>2014–2018</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="E26" t="n">
+        <v>13</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1923,10 +1823,8 @@
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="A27" t="n">
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1943,10 +1841,8 @@
           <t>2013–2022</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
+      <c r="E27" t="n">
+        <v>2</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1980,10 +1876,8 @@
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="A28" t="n">
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2000,10 +1894,8 @@
           <t>2023–ON</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
+      <c r="E28" t="n">
+        <v>2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2053,10 +1945,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="A29" t="n">
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2073,10 +1963,8 @@
           <t>1974–1980</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
+      <c r="E29" t="n">
+        <v>3</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2114,10 +2002,8 @@
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="A30" t="n">
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2134,10 +2020,8 @@
           <t>1981–1992</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
+      <c r="E30" t="n">
+        <v>4</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2179,10 +2063,8 @@
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="A31" t="n">
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2199,10 +2081,8 @@
           <t>1984 ke atas</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
+      <c r="E31" t="n">
+        <v>4</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2240,10 +2120,8 @@
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="A32" t="n">
+        <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2260,10 +2138,8 @@
           <t>2008–2017</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
+      <c r="E32" t="n">
+        <v>4</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2305,10 +2181,8 @@
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="A33" t="n">
+        <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2325,10 +2199,8 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="E33" t="n">
+        <v>10</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2366,10 +2238,8 @@
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+      <c r="A34" t="n">
+        <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2386,10 +2256,8 @@
           <t>2004 – 2019</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
+      <c r="E34" t="n">
+        <v>5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2431,10 +2299,8 @@
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+      <c r="A35" t="n">
+        <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2451,10 +2317,8 @@
           <t xml:space="preserve">2004 – 2012 </t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
+      <c r="E35" t="n">
+        <v>4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2496,10 +2360,8 @@
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="A36" t="n">
+        <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2516,10 +2378,8 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="E36" t="n">
+        <v>13</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2561,10 +2421,8 @@
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="A37" t="n">
+        <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2581,10 +2439,8 @@
           <t>2022-2026</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
+      <c r="E37" t="n">
+        <v>9</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2626,10 +2482,8 @@
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="A38" t="n">
+        <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2646,10 +2500,8 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
+      <c r="E38" t="n">
+        <v>3</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2691,10 +2543,8 @@
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="A39" t="n">
+        <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2711,10 +2561,8 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="E39" t="n">
+        <v>14</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2756,10 +2604,8 @@
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="A40" t="n">
+        <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2776,10 +2622,8 @@
           <t>2017–2020</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="E40" t="n">
+        <v>10</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2821,10 +2665,8 @@
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="A41" t="n">
+        <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2841,10 +2683,8 @@
           <t>2021–2026</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="E41" t="n">
+        <v>10</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2886,10 +2726,8 @@
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
+      <c r="A42" t="n">
+        <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2906,10 +2744,8 @@
           <t>2019-On</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
+      <c r="E42" t="n">
+        <v>9</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2955,10 +2791,8 @@
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="A43" t="n">
+        <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2975,10 +2809,8 @@
           <t>2022-On</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="E43" t="n">
+        <v>10</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3024,10 +2856,8 @@
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="A44" t="n">
+        <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -3044,10 +2874,8 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="E44" t="n">
+        <v>13</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3089,10 +2917,8 @@
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="A45" t="n">
+        <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -3109,10 +2935,8 @@
           <t xml:space="preserve">2025 (2024 Cina) </t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="E45" t="n">
+        <v>17</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/data_cover.xlsx
+++ b/data_cover.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,8 +494,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -512,8 +514,10 @@
           <t>2016 – 2021</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>10</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -547,8 +551,10 @@
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -565,8 +571,10 @@
           <t>2022-ON</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>10</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -600,8 +608,10 @@
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -618,8 +628,10 @@
           <t>2021-ON</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -653,8 +665,10 @@
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -671,8 +685,10 @@
           <t>2006-2013</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>5</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -706,8 +722,10 @@
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -724,8 +742,10 @@
           <t>2014-2017</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>4</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -759,8 +779,10 @@
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -777,8 +799,10 @@
           <t>2023-ON</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>9</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -812,8 +836,10 @@
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -830,8 +856,10 @@
           <t xml:space="preserve">2017 – 2020 </t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>8</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -865,8 +893,10 @@
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -883,8 +913,10 @@
           <t>2021 – 2023</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>8</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -918,8 +950,10 @@
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -936,8 +970,10 @@
           <t>1998-2007</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>14</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -971,8 +1007,10 @@
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -989,8 +1027,10 @@
           <t>2019-2024</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>13</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1024,8 +1064,10 @@
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1042,8 +1084,10 @@
           <t>2012-2018</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>6</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1077,8 +1121,10 @@
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1095,8 +1141,10 @@
           <t>2022-ON</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>10</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1130,8 +1178,10 @@
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1148,8 +1198,10 @@
           <t>2022-ON</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>10</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1179,8 +1231,10 @@
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1197,8 +1251,10 @@
           <t>2001 – 2007</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>6</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1232,8 +1288,10 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1250,8 +1308,10 @@
           <t>2008 – 2013</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>6</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1285,8 +1345,10 @@
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1303,8 +1365,10 @@
           <t>2014 – 2019</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>6</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1338,8 +1402,10 @@
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1356,8 +1422,10 @@
           <t>2019-ON</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>6</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1391,8 +1459,10 @@
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1409,8 +1479,10 @@
           <t>1950 – 1967</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>16</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1444,8 +1516,10 @@
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1462,8 +1536,10 @@
           <t>1967 – 1979</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>16</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1497,8 +1573,10 @@
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1515,8 +1593,10 @@
           <t>2002–2014</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>14</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1550,8 +1630,10 @@
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1568,8 +1650,10 @@
           <t>2015-ON</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>14</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1603,8 +1687,10 @@
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1621,8 +1707,10 @@
           <t>2007-2021</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>11</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1656,8 +1744,10 @@
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1674,8 +1764,10 @@
           <t>2022-ON</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>14</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1709,8 +1801,10 @@
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1727,8 +1821,10 @@
           <t>2018-ON</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>13</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1766,8 +1862,10 @@
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1784,8 +1882,10 @@
           <t>2014–2018</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>13</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1823,8 +1923,10 @@
       <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1841,8 +1943,10 @@
           <t>2013–2022</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>2</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1876,8 +1980,10 @@
       <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1894,8 +2000,10 @@
           <t>2023–ON</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>2</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1945,8 +2053,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1963,8 +2073,10 @@
           <t>1974–1980</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>3</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2002,8 +2114,10 @@
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2020,8 +2134,10 @@
           <t>1981–1992</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>4</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2063,8 +2179,10 @@
       <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2081,8 +2199,10 @@
           <t>1984 ke atas</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>4</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2120,8 +2240,10 @@
       <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2138,8 +2260,10 @@
           <t>2008–2017</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>4</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2181,8 +2305,10 @@
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2199,8 +2325,10 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E33" t="n">
-        <v>10</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2238,8 +2366,10 @@
       <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2256,8 +2386,10 @@
           <t>2004 – 2019</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>5</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2299,8 +2431,10 @@
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2317,8 +2451,10 @@
           <t xml:space="preserve">2004 – 2012 </t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>4</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2360,8 +2496,10 @@
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2378,8 +2516,10 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>13</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2421,8 +2561,10 @@
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2439,8 +2581,10 @@
           <t>2022-2026</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>9</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2482,8 +2626,10 @@
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2500,8 +2646,10 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v>3</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2543,8 +2691,10 @@
       <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2561,8 +2711,10 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="E39" t="n">
-        <v>14</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2604,8 +2756,10 @@
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2622,8 +2776,10 @@
           <t>2017–2020</t>
         </is>
       </c>
-      <c r="E40" t="n">
-        <v>10</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2665,8 +2821,10 @@
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2683,8 +2841,10 @@
           <t>2021–2026</t>
         </is>
       </c>
-      <c r="E41" t="n">
-        <v>10</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2726,8 +2886,10 @@
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2744,8 +2906,10 @@
           <t>2019-On</t>
         </is>
       </c>
-      <c r="E42" t="n">
-        <v>9</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2791,8 +2955,10 @@
       <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2809,8 +2975,10 @@
           <t>2022-On</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v>10</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2856,8 +3024,10 @@
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2874,8 +3044,10 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="E44" t="n">
-        <v>13</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2917,8 +3089,10 @@
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2935,8 +3109,10 @@
           <t xml:space="preserve">2025 (2024 Cina) </t>
         </is>
       </c>
-      <c r="E45" t="n">
-        <v>17</v>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2984,6 +3160,75 @@
           <t>1787883311_Foto4_Screenshot 2026-08-28 091426.png</t>
         </is>
       </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>M9</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>5.145 mm</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1.970 mm</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1.805 mm</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>STANDAR</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Sudah Terdaftar Resmi: Hak paten desain industri dan nama BYD M9 telah resmi terdaftar di Pangkalan Data Kekayaan Intelektual (PDKI) Kemenkumham RI sejak pertengahan 2025.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1787967030_Foto1_Screenshot 2026-08-29 082307.png</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1787967030_Foto2_Screenshot 2026-08-29 080638.png</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1787967030_Foto3_Screenshot 2026-08-29 082318.png</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data_cover.xlsx
+++ b/data_cover.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cosmic Comp\Documents\GitHub\ukuran-cover-mobil\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D808FE8F-4877-4EFE-8EBF-A2362D29BB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32AD77AA-8D6D-42C7-B6E2-C7E6FA9D1D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data_cover.xlsx
+++ b/data_cover.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3364,6 +3364,71 @@
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Sealion 7</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>4.830 mm</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1.925 mm</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>1.620 mm</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>STANDAR</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1788159040_Foto1_Screenshot 2026-08-31 134837.png</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>1788159040_Foto2_Screenshot 2026-08-31 134809.png</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>1788159040_Foto3_Screenshot 2026-08-31 134815.png</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cover.xlsx
+++ b/data_cover.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3429,6 +3429,75 @@
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Lexus UX 200 Sport</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2019-2023</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>4.495 mm</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1.840 mm</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1.520 mm</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>HARUS CUSTOM</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Harus Custom karena spek ukuran diantara no 09 dan 10 ( Bila pakai No 10 kepanjangan dan besar dan bila pakai no 09  juga masih turun ) Info Pak Jamal</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1788321753_Foto1_Screenshot 2026-09-01 180615.png</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>1788321753_Foto2_lexus UX 200 1.jpg</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>1788321753_Foto3_Lexus UX 200.jpg</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cover.xlsx
+++ b/data_cover.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,32 +506,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BRV</t>
+          <t>City HB</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2016 – 2021</t>
+          <t>2021-ON</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4.456 mm</t>
+          <t>4.349 mm</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.735 mm</t>
+          <t>1.748 mm</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.666 mm</t>
+          <t>1.488 mm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Pas dengan ukuran bodi standar. | Terakhir diedit: 15-08-2026 09:47</t>
+          <t>Pas dengan ukuran bodi standar.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -558,37 +558,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Honda</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BRV (NX7)</t>
+          <t>Yaris Bakpao</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2022-ON</t>
+          <t>2006-2013</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4.490 mm</t>
+          <t>3750 mm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.780 mm</t>
+          <t>1.695 mm</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.685 mm</t>
+          <t>1.520 - 1.530 mm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Pas dengan ukuran bodi standar.</t>
+          <t>Pas dengan ukuran bodi standar. | Terakhir diedit: 14-08-2026 13:28</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -615,37 +615,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Honda</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>City HB</t>
+          <t>Yaris Lele</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2021-ON</t>
+          <t>2014-2017</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4.349 mm</t>
+          <t>4.115 mm</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.748 mm</t>
+          <t>1.700 mm</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.488 mm</t>
+          <t>1.475 mm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,32 +677,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Yaris Bakpao</t>
+          <t>Yaris Cross</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2006-2013</t>
+          <t>2023-ON</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3750 mm</t>
+          <t>4.310 mm</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.695 mm</t>
+          <t>1.770 mm</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.520 - 1.530 mm</t>
+          <t>1.615 mm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Pas dengan ukuran bodi standar. | Terakhir diedit: 14-08-2026 13:28</t>
+          <t>Pas dengan ukuran bodi standar.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -729,37 +729,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>BMW</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yaris Lele</t>
+          <t>520i/G30</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2014-2017</t>
+          <t xml:space="preserve">2017 – 2020 </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>4.115 mm</t>
+          <t>4.936 mm</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.700 mm</t>
+          <t>1.868 mm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.475 mm</t>
+          <t>1.466 mm - 1.479 mm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Pas dengan ukuran bodi standar.</t>
+          <t>Fase Pre-facelift: Resmi masuk dan mulai dipasarkan di Indonesia sejak pertengahan 2017</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -786,37 +786,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>BMW</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yaris Cross</t>
+          <t>520i/G60</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2023-ON</t>
+          <t>2021 – 2023</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4.310 mm</t>
+          <t>5.060 mm</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.770 mm</t>
+          <t>1.900 mm</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.615 mm</t>
+          <t>1.515 mm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pas dengan ukuran bodi standar.</t>
+          <t xml:space="preserve">Fase Facelift / LCI </t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -843,37 +843,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>520i/G30</t>
+          <t>LC Cygnus (Seri 100)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017 – 2020 </t>
+          <t>1998-2007</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4.936 mm</t>
+          <t>4.890 mm</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.868 mm</t>
+          <t>1.940 mm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.466 mm - 1.479 mm</t>
+          <t>1.880 mm - 1.890 mm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Fase Pre-facelift: Resmi masuk dan mulai dipasarkan di Indonesia sejak pertengahan 2017</t>
+          <t>Karakteristik:ukuran dimensinya hampir sama persis karena Toyota Land Cruiser Cygnus dan Lexus LX 470 dibangun menggunakan sasis, platform, dan bodi dasar yang sama dari Land Cruiser Seri 100</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -905,32 +905,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>520i/G60</t>
+          <t>320i Touring (G21)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2021 – 2023</t>
+          <t>2019-2024</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5.060 mm</t>
+          <t>4.713 mm</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.900 mm</t>
+          <t>1.827 mm</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.515 mm</t>
+          <t>1.470 mm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fase Facelift / LCI </t>
+          <t>Karakteristik:Model Pre-facelift (Produksi 2019 – 2022) | Model Facelift / LCI 1 (Produksi 2022 – 2024) | Model Facelift / LCI 2 (Produksi 2024 – Sekarang)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -957,37 +957,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>BMW</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LC Cygnus (Seri 100)</t>
+          <t>320i Sedan (F30)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1998-2007</t>
+          <t>2012-2018</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4.890 mm</t>
+          <t>4.633 mm</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.940 mm</t>
+          <t>1.811 mm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.880 mm - 1.890 mm</t>
+          <t>1.429 mm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -997,13 +997,25 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Karakteristik:ukuran dimensinya hampir sama persis karena Toyota Land Cruiser Cygnus dan Lexus LX 470 dibangun menggunakan sasis, platform, dan bodi dasar yang sama dari Land Cruiser Seri 100</t>
+          <t>Karakteristik:Fase Pre | Diedit tgl 2026-09-02 11:32</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1788323520_Foto1_Screenshot 2026-09-02 113055.png</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1788323520_Foto2_Screenshot 2026-09-02 113100.png</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1788323520_Foto3_Screenshot 2026-09-02 113047.png</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1014,37 +1026,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>320i Touring (G21)</t>
+          <t>Avanza Veloz</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2019-2024</t>
+          <t>2022-ON</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4.713 mm</t>
+          <t>4.475 mm</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.827 mm</t>
+          <t>1.750 mm</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.470 mm</t>
+          <t>1.700 mm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1054,7 +1066,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Karakteristik:Model Pre-facelift (Produksi 2019 – 2022) | Model Facelift / LCI 1 (Produksi 2022 – 2024) | Model Facelift / LCI 2 (Produksi 2024 – Sekarang)</t>
+          <t>Karakteristik:Meskipun dibangun di atas platform sasis yang sama (DNGA / Daihatsu New Global Architecture) dan memiliki wheelbase yang identik, Toyota mendesain bodi Veloz 2022 sedikit lebih bongsor dan kekar dibanding Avanza biasa untuk mengejar visual ala SUV crossover.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1071,37 +1083,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>320i Sedan (F30)</t>
+          <t xml:space="preserve">Avanza </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2012-2018</t>
+          <t>2022-ON</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4.633 mm</t>
+          <t>4.395 mm</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.811 mm</t>
+          <t>1.730mm</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.429 mm</t>
+          <t>1.700 mm (Tipe 1.5)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1109,11 +1121,7 @@
           <t>STANDAR</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Karakteristik:Fase Pre-facelift / Mesin N20 (Produksi 2012 – 2015) | Fase Facelift / LCI – Mesin B48 (Produksi 2015 – 2018)</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -1133,42 +1141,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avanza Veloz</t>
+          <t>Corolla Altis Old</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2022-ON</t>
+          <t>2001 – 2007</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4.475 mm</t>
+          <t>4.530 mm</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.750 mm</t>
+          <t>1.705 mm</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.700 mm</t>
+          <t>1.500 mm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>STANDAR</t>
+          <t>STANDAR | Masih Bisa No 05</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Karakteristik:Meskipun dibangun di atas platform sasis yang sama (DNGA / Daihatsu New Global Architecture) dan memiliki wheelbase yang identik, Toyota mendesain bodi Veloz 2022 sedikit lebih bongsor dan kekar dibanding Avanza biasa untuk mengejar visual ala SUV crossover.</t>
+          <t>Karakteristik: Generasi pertama ini memindahkan citra Corolla dari sedan kompak menjadi sedan medium bernuansa mewah nan elegan. Mesin andalannya berkode 1ZZ-FE 1.800 cc yang pertama kali mengenalkan teknologi VVT-i di kelasnya.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1190,40 +1198,44 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avanza </t>
+          <t>Corolla Altis New</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2022-ON</t>
+          <t>2008 – 2013</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4.395 mm</t>
+          <t>4.540 mm</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1.730mm</t>
+          <t>1.760 mm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.700 mm (Tipe 1.5)</t>
+          <t xml:space="preserve"> 1.465 mm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>STANDAR</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t xml:space="preserve">STANDAR | </t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Karakteristik: Bodinya melebar 55 mm dibanding generasi awal demi kabin yang lebih lapang. Mengadopsi mesin Dual VVT-i dengan dua pilihan opsi mesin di Indonesia, yaitu 1.8L (2ZR-FE) dan varian kencang 2.0L (3ZR-FE) lengkap dengan paddle shift</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
@@ -1243,12 +1255,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Corolla Altis Old</t>
+          <t>Corolla Altis All New</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2001 – 2007</t>
+          <t>2014 – 2019</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1258,27 +1270,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4.530 mm</t>
+          <t>4.620 mm</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.705 mm</t>
+          <t>1.776 mm</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.500 mm</t>
+          <t xml:space="preserve"> 1.460 mm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>STANDAR | Masih Bisa No 05</t>
+          <t>STANDAR</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Karakteristik: Generasi pertama ini memindahkan citra Corolla dari sedan kompak menjadi sedan medium bernuansa mewah nan elegan. Mesin andalannya berkode 1ZZ-FE 1.800 cc yang pertama kali mengenalkan teknologi VVT-i di kelasnya.</t>
+          <t>Karakteristik: Dimensinya melar signifikan (panjang bertambah 80 mm) dan sumbu roda bertambah panjang 100 mm, membuat ruang kaki di baris kedua menjadi yang paling lega di kelasnya saat itu. Desain eksteriornya berubah menjadi jauh lebih tajam, sporty, dan agresi</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1300,12 +1312,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Corolla Altis New</t>
+          <t>Corolla Altis All New G12</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2008 – 2013</t>
+          <t>2019-ON</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1315,27 +1327,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4.540 mm</t>
+          <t>4.630 mm</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.760 mm</t>
+          <t>1.780 mm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.465 mm</t>
+          <t xml:space="preserve"> 1.435 mm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">STANDAR | </t>
+          <t>STANDAR</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Karakteristik: Bodinya melebar 55 mm dibanding generasi awal demi kabin yang lebih lapang. Mengadopsi mesin Dual VVT-i dengan dua pilihan opsi mesin di Indonesia, yaitu 1.8L (2ZR-FE) dan varian kencang 2.0L (3ZR-FE) lengkap dengan paddle shift</t>
+          <t>Karakteristik: Dibangun di atas platform global baru Toyota bernama TNGA (Toyota New Global Architecture). Ukuran bodinya dibuat sedikit lebih panjang dan lebar, namun tingginya dipangkas lebih rendah 25 mm agar menghasilkan pusat gravitasi yang stabil (sporty handling). Generasi ini juga pertama kalinya membawa teknologi mesin Hybrid (2ZR-FXE) yang sangat efisien bahan bakar ke Indonesia. [1, 2, 3, 4, 5]</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1352,47 +1364,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>VW</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Corolla Altis All New</t>
+          <t>Kombi Dakota T1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2014 – 2019</t>
+          <t>1950 – 1967</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4.620 mm</t>
+          <t>4.280 mm</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.776 mm</t>
+          <t>1.720 mm</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.460 mm</t>
+          <t>1.940mm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>STANDAR</t>
+          <t>HARUS CUSTOM</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Karakteristik: Dimensinya melar signifikan (panjang bertambah 80 mm) dan sumbu roda bertambah panjang 100 mm, membuat ruang kaki di baris kedua menjadi yang paling lega di kelasnya saat itu. Desain eksteriornya berubah menjadi jauh lebih tajam, sporty, dan agresi</t>
+          <t>Karakteristik : Merupakan generasi pertama yang sangat ikonik dengan kaca depan terbelah menjadi dua bagian (split window).</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1409,47 +1421,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>VW</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Corolla Altis All New G12</t>
+          <t>Kombi Reguler T2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2019-ON</t>
+          <t>1967 – 1979</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>4.630 mm</t>
+          <t>4.505 mm</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.780 mm</t>
+          <t>1.720 mm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.435 mm</t>
+          <t xml:space="preserve">1.955 mm - 2.040 </t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>STANDAR</t>
+          <t>HARUS CUSTOM</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Karakteristik: Dibangun di atas platform global baru Toyota bernama TNGA (Toyota New Global Architecture). Ukuran bodinya dibuat sedikit lebih panjang dan lebar, namun tingginya dipangkas lebih rendah 25 mm agar menghasilkan pusat gravitasi yang stabil (sporty handling). Generasi ini juga pertama kalinya membawa teknologi mesin Hybrid (2ZR-FXE) yang sangat efisien bahan bakar ke Indonesia. [1, 2, 3, 4, 5]</t>
+          <t>Karakteristik :Menggunakan pintu tengah model geser (sliding door) dan memiliki jendela samping berukuran besar (3 bilah kaca panjang)</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1466,47 +1478,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VW</t>
+          <t xml:space="preserve">Volvo </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kombi Dakota T1</t>
+          <t>XC90 Gen 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1950 – 1967</t>
+          <t>2002–2014</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4.280 mm</t>
+          <t>4.798 mm</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.720 mm</t>
+          <t>1.898 mm</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.940mm</t>
+          <t>1.784 mm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>HARUS CUSTOM</t>
+          <t>STANDAR</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Karakteristik : Merupakan generasi pertama yang sangat ikonik dengan kaca depan terbelah menjadi dua bagian (split window).</t>
+          <t>Karakteristik: Model bekasnya masih cukup dicari di Indonesia (terutama varian mesin bensin 2.5T Turbo atau 2.9 T6 Twin-Turbo) karena kenyamanan suspensinya dan harga bekasnya yang sudah sangat terjangkau</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1523,47 +1535,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VW</t>
+          <t xml:space="preserve">Volvo </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kombi Reguler T2</t>
+          <t>XC90 Gen 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1967 – 1979</t>
+          <t>2015-ON</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4.505 mm</t>
+          <t>4.953 mm</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.720 mm</t>
+          <t>1.931 mm</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.955 mm - 2.040 </t>
+          <t>1.773 mm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>HARUS CUSTOM</t>
+          <t>STANDAR</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Karakteristik :Menggunakan pintu tengah model geser (sliding door) dan memiliki jendela samping berukuran besar (3 bilah kaca panjang)</t>
+          <t>Jarak Terendah ke Tanah (Ground Clearance): Berada di angka 223 mm - 238 mm. Namun, tipe tertinggi yang beredar di Indonesia (seperti Volvo XC90 Ultra atau T8 Recharge) sudah dilengkapi Air Suspension (suspensi udara) otomatis. Ketinggian mobil bisa turun sendiri saat melaju kencang di mode Power, atau naik saat mengaktifkan mode Off-road.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1580,37 +1592,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Volvo </t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>XC90 Gen 1</t>
+          <t>LC VX 200</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2002–2014</t>
+          <t>2007-2021</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4.798 mm</t>
+          <t>4.950 mm</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.898 mm</t>
+          <t>1.970 mm</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.784 mm</t>
+          <t>1.905 mm – 1.945 mm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1620,7 +1632,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Karakteristik: Model bekasnya masih cukup dicari di Indonesia (terutama varian mesin bensin 2.5T Turbo atau 2.9 T6 Twin-Turbo) karena kenyamanan suspensinya dan harga bekasnya yang sudah sangat terjangkau</t>
+          <t>Mobil yang dijuluki sebagai "King of the Offroad" ini diproduksi secara global mulai tahun 2007 hingga 2021 sebelum akhirnya digantikan oleh Seri 300</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1637,17 +1649,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Volvo </t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>XC90 Gen 2</t>
+          <t>Zenix Modelista</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2015-ON</t>
+          <t>2022-ON</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1657,27 +1669,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4.953 mm</t>
+          <t>4.755 mm</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.931 mm</t>
+          <t>1.850 mm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.773 mm</t>
+          <t>1.795 mm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>STANDAR</t>
+          <t xml:space="preserve">STANDAR | </t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Jarak Terendah ke Tanah (Ground Clearance): Berada di angka 223 mm - 238 mm. Namun, tipe tertinggi yang beredar di Indonesia (seperti Volvo XC90 Ultra atau T8 Recharge) sudah dilengkapi Air Suspension (suspensi udara) otomatis. Ketinggian mobil bisa turun sendiri saat melaju kencang di mode Power, atau naik saat mengaktifkan mode Off-road.</t>
+          <t xml:space="preserve">Varian Modellista: Memiliki panjang eksterior aktual sedikit lebih maju pada bumper depan dan belakang karena penambahan aksesori body kit resmi (Front &amp; Rear Bumper Spoiler). Sisi bawah bumper depan juga terasa sedikit lebih rendah ke tanah akibat penambahan komponen tersebut, meskipun tinggi sasis ground clearance tengahnya tetap sama di angka 185 mm. Varian Non-Modellista (Standar): Menggunakan bentuk bumper bawaan pabrik yang bersih tanpa tambahan bodi plastik lips di bagian bawah depan, samping, maupun belakang. Modelista Ada Bodykit ukuran sempat bermasalah pakai no 14 </t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1694,51 +1706,55 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>BMW</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LC VX 200</t>
+          <t>X4/G02</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2007-2021</t>
+          <t>2018-ON</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4.950 mm</t>
+          <t>4.752 mm</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.970 mm</t>
+          <t>1.918 mm</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.905 mm – 1.945 mm</t>
+          <t>1.621 mm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>STANDAR</t>
+          <t>HARUS CUSTOM |</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Mobil yang dijuluki sebagai "King of the Offroad" ini diproduksi secara global mulai tahun 2007 hingga 2021 sebelum akhirnya digantikan oleh Seri 300</t>
+          <t>Proporsi dan Aerodinamika: Generasi kedua terlihat jauh lebih proporsional dengan atap bagian belakang yang melandai lebih halus (fluid), mengurangi koefisien seret udara (Cd) sebesar 10%. | Terakhir diedit: 15-08-2026 10:11</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1786763475_Foto1_bmw-x4.jpg</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -1751,51 +1767,55 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>BMW</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Zenix Modelista</t>
+          <t>X4/F26</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2022-ON</t>
+          <t>2014–2018</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4.755 mm</t>
+          <t>4.671 mm</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.850 mm</t>
+          <t>1.881 mm</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.795 mm</t>
+          <t>1.624 mm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">STANDAR | </t>
+          <t>HARUS CUSTOM |</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Varian Modellista: Memiliki panjang eksterior aktual sedikit lebih maju pada bumper depan dan belakang karena penambahan aksesori body kit resmi (Front &amp; Rear Bumper Spoiler). Sisi bawah bumper depan juga terasa sedikit lebih rendah ke tanah akibat penambahan komponen tersebut, meskipun tinggi sasis ground clearance tengahnya tetap sama di angka 185 mm. Varian Non-Modellista (Standar): Menggunakan bentuk bumper bawaan pabrik yang bersih tanpa tambahan bodi plastik lips di bagian bawah depan, samping, maupun belakang. Modelista Ada Bodykit ukuran sempat bermasalah pakai no 14 </t>
+          <t>Harus custom : Karena Bagian belakang Aerodinamika | Terakhir diedit: 15-08-2026 10:12</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1786763551_Foto1_bmw-x4.jpg</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -1808,55 +1828,51 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>Daihatsu</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>X4/G02</t>
+          <t>Ayla G1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2018-ON</t>
+          <t>2013–2022</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>4.752 mm</t>
+          <t>3.640 mm – 3.660 mm</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.918 mm</t>
+          <t>1.600 mm</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.621 mm</t>
+          <t>1.520 mm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>HARUS CUSTOM |</t>
+          <t>STANDAR</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Proporsi dan Aerodinamika: Generasi kedua terlihat jauh lebih proporsional dengan atap bagian belakang yang melandai lebih halus (fluid), mengurangi koefisien seret udara (Cd) sebesar 10%. | Terakhir diedit: 15-08-2026 10:11</t>
+          <t>Ingat : Beda ukuran dengan Gen 2 : Lebih panjang hingga 120 mm | Lebih lebar 65 mm | Lebih rendah 5 mm</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>1786763475_Foto1_bmw-x4.jpg</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -1869,58 +1885,70 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>Daihatsu</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>X4/F26</t>
+          <t>Ayla G2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2014–2018</t>
+          <t>2023–ON</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4.671 mm</t>
+          <t>3.760 mm</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.881 mm</t>
+          <t>1.665 mm</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.624 mm</t>
+          <t>1.515 mm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>HARUS CUSTOM |</t>
+          <t>STANDAR</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Harus custom : Karena Bagian belakang Aerodinamika | Terakhir diedit: 15-08-2026 10:12</t>
+          <t>Kabin Lebih Lapang: Penambahan panjang dan lebar pada generasi kedua berkat penggunaan sasis baru DNGA membuat ruang kaki (legroom) dan ruang bahu (shoulder room) jauh lebih luas | Terakhir diedit: 15-08-2026 09:51</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1786763551_Foto1_bmw-x4.jpg</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+          <t>Ayla 2024.jpg</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1786762291_Foto2_Ayla 2024 1.jpg</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1786762291_Foto3_Ayla 2024 2.jpg</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1786762291_Foto4_Ayla 2024 3.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1930,37 +1958,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Daihatsu</t>
+          <t>VW</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ayla G1</t>
+          <t>Scirocco MK1 Old</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2013–2022</t>
+          <t>1974–1980</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>3.640 mm – 3.660 mm</t>
+          <t>3.850 mm – 3.885 mm</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.600 mm</t>
+          <t>1.620 mm – 1.625 mm</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.520 mm</t>
+          <t>1.309 mm – 1.310 mm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1970,11 +1998,15 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Ingat : Beda ukuran dengan Gen 2 : Lebih panjang hingga 120 mm | Lebih lebar 65 mm | Lebih rendah 5 mm</t>
+          <t>Catatan: Variasi kecil pada panjang bodi dipengaruhi oleh perubahan desain bumper, terutama setelah versi facelift besar pada tahun 1977 yang menggunakan bumper berlapis plastik lebih tebal.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1787279323_Foto1_Screenshot 2026-08-21 092506.png</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -1987,37 +2019,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Daihatsu</t>
+          <t>VW</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ayla G2</t>
+          <t xml:space="preserve">Scirocco MK2 </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2023–ON</t>
+          <t>1981–1992</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>3.760 mm</t>
+          <t>4.050 mm</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.665 mm</t>
+          <t>1.625 mm – 1.645 mm</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.515 mm</t>
+          <t>1.310 mm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2027,30 +2059,22 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Kabin Lebih Lapang: Penambahan panjang dan lebar pada generasi kedua berkat penggunaan sasis baru DNGA membuat ruang kaki (legroom) dan ruang bahu (shoulder room) jauh lebih luas | Terakhir diedit: 15-08-2026 09:51</t>
+          <t xml:space="preserve">Perhatian : Ada Yang Versi Body Kit / Facelift </t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Ayla 2024.jpg</t>
+          <t>1787280348_Foto1_Screenshot 2026-08-21 093839.png</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1786762291_Foto2_Ayla 2024 1.jpg</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>1786762291_Foto3_Ayla 2024 2.jpg</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>1786762291_Foto4_Ayla 2024 3.jpg</t>
-        </is>
-      </c>
+          <t>1787280348_Foto2_Screenshot 2026-08-21 093936.png</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2065,32 +2089,32 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scirocco MK1 Old</t>
+          <t>Scirocco MK2  Versi Body Kit / Facelift</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1974–1980</t>
+          <t>1984 ke atas</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3.850 mm – 3.885 mm</t>
+          <t>4.050 mm</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.620 mm – 1.625 mm</t>
+          <t>1.645 mm</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.309 mm – 1.310 mm</t>
+          <t>1.280 mm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2100,13 +2124,13 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Catatan: Variasi kecil pada panjang bodi dipengaruhi oleh perubahan desain bumper, terutama setelah versi facelift besar pada tahun 1977 yang menggunakan bumper berlapis plastik lebih tebal.</t>
+          <t>(Bisa sedikit lebih panjang di area ujung bumper) | Terakhir diedit: 21-08-2026 09:51</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1787279323_Foto1_Screenshot 2026-08-21 092506.png</t>
+          <t>1787280700_Foto1_Screenshot 2026-08-21 093936.png</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -2126,12 +2150,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scirocco MK2 </t>
+          <t>Scirocco MK3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1981–1992</t>
+          <t>2008–2017</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2141,38 +2165,38 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4.050 mm</t>
+          <t>4.256 mm</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.625 mm – 1.645 mm</t>
+          <t>1.810 mm – 1.820 mm</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.310 mm</t>
+          <t>1.404 mm – 1.406 mm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>STANDAR</t>
+          <t>SARAN DICUTOM (NGEPRES)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perhatian : Ada Yang Versi Body Kit / Facelift </t>
+          <t>Berubah total menjadi hatchback coupé modern berotot. Generasi ini yang masuk ke Indonesia dan menawarkan pilihan mesin dari 1.4 TSI, 2.0 TSI (GT), hingga versi monster Scirocco R | Terakhir diedit: 21-08-2026 10:05</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1787280348_Foto1_Screenshot 2026-08-21 093839.png</t>
+          <t>1787281508_Foto1_Screenshot 2026-08-21 095854.png</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1787280348_Foto2_Screenshot 2026-08-21 093936.png</t>
+          <t>1787281508_Foto2_Screenshot 2026-08-21 095913.png</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -2186,37 +2210,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VW</t>
+          <t>Jaecoo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scirocco MK2  Versi Body Kit / Facelift</t>
+          <t>J5 EV</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1984 ke atas</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4.050 mm</t>
+          <t>4.380 mm</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.645 mm</t>
+          <t>1.860 mm</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.280 mm</t>
+          <t>1.650 mm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2224,18 +2248,18 @@
           <t>STANDAR</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>(Bisa sedikit lebih panjang di area ujung bumper) | Terakhir diedit: 21-08-2026 09:51</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1787280700_Foto1_Screenshot 2026-08-21 093936.png</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
+          <t>1787290338_Foto1_Screenshot 2026-08-21 122915.png</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>1787290338_Foto2_Screenshot 2026-08-21 123147.png</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
     </row>
@@ -2247,58 +2271,58 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>VW</t>
+          <t xml:space="preserve">Nissan </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scirocco MK3</t>
+          <t>Latio Sedan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2008–2017</t>
+          <t>2004 – 2019</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>4.256 mm</t>
+          <t>4.430 mm</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.810 mm – 1.820 mm</t>
+          <t>1.695 mm</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.404 mm – 1.406 mm</t>
+          <t>1.535 mm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SARAN DICUTOM (NGEPRES)</t>
+          <t>STANDAR</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Berubah total menjadi hatchback coupé modern berotot. Generasi ini yang masuk ke Indonesia dan menawarkan pilihan mesin dari 1.4 TSI, 2.0 TSI (GT), hingga versi monster Scirocco R | Terakhir diedit: 21-08-2026 10:05</t>
+          <t>Produksi : Dilanjutkan gen-2 N17 khusus sedan</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1787281508_Foto1_Screenshot 2026-08-21 095854.png</t>
+          <t>1787292517_Foto1_Screenshot 2026-08-21 130755.png</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1787281508_Foto2_Screenshot 2026-08-21 095913.png</t>
+          <t>1787292517_Foto2_Screenshot 2026-08-21 130815.png</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -2312,37 +2336,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jaecoo</t>
+          <t xml:space="preserve">Nissan </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>J5 EV</t>
+          <t>Latio HB</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t xml:space="preserve">2004 – 2012 </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4.380 mm</t>
+          <t>4.205 mm - 4.250 mm</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.860 mm</t>
+          <t>1.695 mm</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.650 mm</t>
+          <t>1.530 mm - 1.535 mm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2350,16 +2374,20 @@
           <t>STANDAR</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Dihentikan dan diganti oleh Nissan Note | Nama "Latio" untuk versi Hatchback disuntik mati lebih cepat secara global</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1787290338_Foto1_Screenshot 2026-08-21 122915.png</t>
+          <t>1787292869_Foto1_Screenshot 2026-08-21 131339.png</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1787290338_Foto2_Screenshot 2026-08-21 123147.png</t>
+          <t>1787292869_Foto2_Screenshot 2026-08-21 131412.png</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -2373,37 +2401,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nissan </t>
+          <t>Mitsubishi</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latio Sedan</t>
+          <t>Destinator</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2004 – 2019</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>4.430 mm</t>
+          <t>4.680 mm</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.695 mm</t>
+          <t>1.840 mm</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.535 mm</t>
+          <t>1.780 mm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2413,18 +2441,18 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Produksi : Dilanjutkan gen-2 N17 khusus sedan</t>
+          <t>Semua Tipe Sama Ukurannya</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1787292517_Foto1_Screenshot 2026-08-21 130755.png</t>
+          <t>1787300320_Foto1_Screenshot 2026-08-21 151803.png</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1787292517_Foto2_Screenshot 2026-08-21 130815.png</t>
+          <t>1787300320_Foto2_Screenshot 2026-08-21 151815.png</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -2438,37 +2466,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nissan </t>
+          <t>BYD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latio HB</t>
+          <t>Atto 3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004 – 2012 </t>
+          <t>2022-2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4.205 mm - 4.250 mm</t>
+          <t>4.455 mm</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.695 mm</t>
+          <t>1.875 mm</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.530 mm - 1.535 mm</t>
+          <t>1.615 mm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2478,18 +2506,18 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Dihentikan dan diganti oleh Nissan Note | Nama "Latio" untuk versi Hatchback disuntik mati lebih cepat secara global</t>
+          <t xml:space="preserve"> Ukuran dimensi luar BYD Atto 3 model tahun 2022 dan model terbaru tahun 2026 adalah sama persis</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1787292869_Foto1_Screenshot 2026-08-21 131339.png</t>
+          <t>1787370608_Foto1_Screenshot 2026-08-22 104930.png</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1787292869_Foto2_Screenshot 2026-08-21 131412.png</t>
+          <t>1787370608_Foto2_Screenshot 2026-08-22 104936.png</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -2503,12 +2531,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mitsubishi</t>
+          <t>BYD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Destinator</t>
+          <t>Atto 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2518,22 +2546,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4.680 mm</t>
+          <t>3.780 mm</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.840 mm</t>
+          <t>1.715 mm</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.780 mm</t>
+          <t>1.540 mm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2543,18 +2571,18 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Semua Tipe Sama Ukurannya</t>
+          <t>Di beberapa pasar global juga dikenal sebagai BYD Seagull</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1787300320_Foto1_Screenshot 2026-08-21 151803.png</t>
+          <t>1787371026_Foto1_Screenshot 2026-08-22 105614.png</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1787300320_Foto2_Screenshot 2026-08-21 151815.png</t>
+          <t>1787371026_Foto2_Screenshot 2026-08-22 105621.png</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -2568,37 +2596,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BYD</t>
+          <t>Xpeng</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atto 3</t>
+          <t>G6 Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2022-2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4.455 mm</t>
+          <t>4.758 mm</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.875 mm</t>
+          <t>1.920 mm</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.615 mm</t>
+          <t>1.650 mm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2608,18 +2636,18 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ukuran dimensi luar BYD Atto 3 model tahun 2022 dan model terbaru tahun 2026 adalah sama persis</t>
+          <t>Aerodinamis | XPENG G6 Pro memiliki ukuran bodi yang jauh lebih besar dan masuk ke dalam kategori Mid-Size Coupe SUV</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1787370608_Foto1_Screenshot 2026-08-22 104930.png</t>
+          <t>1787371401_Foto1_Screenshot 2026-08-22 110140.png</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1787370608_Foto2_Screenshot 2026-08-22 104936.png</t>
+          <t>1787371401_Foto2_Screenshot 2026-08-22 110130.png</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -2633,37 +2661,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BYD</t>
+          <t>Mitsubishi</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atto 1</t>
+          <t>Xpander</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2017–2020</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3.780 mm</t>
+          <t>4.475 mm</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.715 mm</t>
+          <t>1.750 mm</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.540 mm</t>
+          <t>1.700 mm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2673,18 +2701,18 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Di beberapa pasar global juga dikenal sebagai BYD Seagull</t>
+          <t>Semua Tipe Xpander Pakai No 10 (2017-2026)</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1787371026_Foto1_Screenshot 2026-08-22 105614.png</t>
+          <t>1787373483_Foto1_Screenshot 2026-08-22 113720.png</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1787371026_Foto2_Screenshot 2026-08-22 105621.png</t>
+          <t>1787373483_Foto2_Screenshot 2026-08-22 113727.png</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -2698,37 +2726,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Xpeng</t>
+          <t>Mitsubishi</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>G6 Pro</t>
+          <t>Xpander New (Facelift)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021–2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4.758 mm</t>
+          <t>4.595 mm</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.920 mm</t>
+          <t>1.750 mm</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.650 mm</t>
+          <t>1.750 mm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2738,18 +2766,18 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Aerodinamis | XPENG G6 Pro memiliki ukuran bodi yang jauh lebih besar dan masuk ke dalam kategori Mid-Size Coupe SUV</t>
+          <t>Ukuran bodi luar Mitsubishi Xpander dari tahun 2017 hingga 2026 mengalami perubahan ukuran menjadi lebih panjang dan lebih tinggi</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1787371401_Foto1_Screenshot 2026-08-22 110140.png</t>
+          <t>1787373893_Foto1_Screenshot 2026-08-22 114430.png</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1787371401_Foto2_Screenshot 2026-08-22 110130.png</t>
+          <t>1787373893_Foto2_Screenshot 2026-08-22 114436.png</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -2768,32 +2796,32 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Xpander</t>
+          <t>Eclipse Cross</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2017–2020</t>
+          <t>2019-On</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>4.475 mm</t>
+          <t>4.405 mm</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.750 mm</t>
+          <t>1.805 mm</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.700 mm</t>
+          <t>1.674 mm -1.685 mm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2803,21 +2831,25 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Semua Tipe Xpander Pakai No 10 (2017-2026)</t>
+          <t>Secara garis besar untuk pasar Indonesia, semua tipe Mitsubishi Eclipse Cross memiliki dimensi panjang dan lebar yang sama, yaitu panjang 4.405 mm dan lebar 1.805 mm. Kecuali tingginya | Terakhir diedit: 26-08-2026 09:04</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1787373483_Foto1_Screenshot 2026-08-22 113720.png</t>
+          <t>1787709451_Foto1_Screenshot 2026-08-26 085628.png</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1787373483_Foto2_Screenshot 2026-08-22 113727.png</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>1787709451_Foto2_Screenshot 2026-08-26 085635.png</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1787709451_Foto3_Screenshot 2026-08-26 085641.png</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
@@ -2828,17 +2860,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mitsubishi</t>
+          <t>Hyundai</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Xpander New (Facelift)</t>
+          <t>Stargazer X</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2021–2026</t>
+          <t>2022-On</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2848,17 +2880,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4.595 mm</t>
+          <t>4.460 mm</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.750 mm</t>
+          <t>1.780 mm</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1.750 mm</t>
+          <t>1.690 – 1.695 mm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2868,21 +2900,25 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Ukuran bodi luar Mitsubishi Xpander dari tahun 2017 hingga 2026 mengalami perubahan ukuran menjadi lebih panjang dan lebih tinggi</t>
+          <t>Secara umum, dimensi dasar untuk varian standar Hyundai Stargazer keluaran tahun 2022 hingga model penyegaran di tahun 2025 adalah sama | Terakhir diedit: 26-08-2026 09:28</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1787373893_Foto1_Screenshot 2026-08-22 114430.png</t>
+          <t>1787711165_Foto1_Screenshot 2026-08-26 092522.png</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1787373893_Foto2_Screenshot 2026-08-22 114436.png</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>1787711165_Foto2_Screenshot 2026-08-26 092528.png</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1787711283_Foto3_Screenshot 2026-08-26 092717.png</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -2893,37 +2929,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mitsubishi</t>
+          <t>Hyundai</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Eclipse Cross</t>
+          <t>Stargazer Cartenz X</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2019-On</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>4.405 mm</t>
+          <t>4.610 mm</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1.805 mm</t>
+          <t>1.820 mm</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.674 mm -1.685 mm</t>
+          <t>1.740 mm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2931,25 +2967,21 @@
           <t>STANDAR</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Secara garis besar untuk pasar Indonesia, semua tipe Mitsubishi Eclipse Cross memiliki dimensi panjang dan lebar yang sama, yaitu panjang 4.405 mm dan lebar 1.805 mm. Kecuali tingginya | Terakhir diedit: 26-08-2026 09:04</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1787709451_Foto1_Screenshot 2026-08-26 085628.png</t>
+          <t>1787711964_Foto1_Screenshot 2026-08-26 093746.png</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1787709451_Foto2_Screenshot 2026-08-26 085635.png</t>
+          <t>1787711964_Foto2_Screenshot 2026-08-26 093808.png</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1787709451_Foto3_Screenshot 2026-08-26 085641.png</t>
+          <t>1787711964_Foto3_Screenshot 2026-08-26 093910.png</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
@@ -2962,66 +2994,70 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hyundai</t>
+          <t>Xpeng</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Stargazer X</t>
+          <t>X9</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2022-On</t>
+          <t xml:space="preserve">2025 (2024 Cina) </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4.460 mm</t>
+          <t>5.293 mm – 5.316 mm</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1.780 mm</t>
+          <t>1.988 mm</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1.690 – 1.695 mm</t>
+          <t>1.785 mm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>STANDAR</t>
+          <t>HARUS CUSTOM</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Secara umum, dimensi dasar untuk varian standar Hyundai Stargazer keluaran tahun 2022 hingga model penyegaran di tahun 2025 adalah sama | Terakhir diedit: 26-08-2026 09:28</t>
+          <t xml:space="preserve">Kalau 17 Durable Premium Pas Sekali | Pernah Coba Xtrem 17 Malah Ketat | </t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1787711165_Foto1_Screenshot 2026-08-26 092522.png</t>
+          <t>1787883311_Foto1_Screenshot 2026-08-28 091244.png</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1787711165_Foto2_Screenshot 2026-08-26 092528.png</t>
+          <t>1787883311_Foto2_Screenshot 2026-08-28 091307.png</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>1787711283_Foto3_Screenshot 2026-08-26 092717.png</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr"/>
+          <t>1787883311_Foto3_Screenshot 2026-08-28 091336.png</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1787883311_Foto4_Screenshot 2026-08-28 091426.png</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3031,59 +3067,63 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hyundai</t>
+          <t>BYD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Stargazer Cartenz X</t>
+          <t>M9</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>4.610 mm</t>
+          <t>5.145 mm</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.820 mm</t>
+          <t>1.970 mm</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.740 mm</t>
+          <t>1.805 mm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>STANDAR</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>HARUS CUSTOM</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sudah Terdaftar Resmi: Hak paten desain industri dan nama BYD M9 telah resmi terdaftar di Pangkalan Data Kekayaan Intelektual (PDKI) Kemenkumham RI sejak pertengahan 2025.</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1787711964_Foto1_Screenshot 2026-08-26 093746.png</t>
+          <t>1787967030_Foto1_Screenshot 2026-08-29 082307.png</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1787711964_Foto2_Screenshot 2026-08-26 093808.png</t>
+          <t>1787967030_Foto2_Screenshot 2026-08-29 080638.png</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1787711964_Foto3_Screenshot 2026-08-26 093910.png</t>
+          <t>1787967030_Foto3_Screenshot 2026-08-29 082318.png</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
@@ -3096,70 +3136,66 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Xpeng</t>
+          <t>BYD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>X9</t>
+          <t>M6 EV / DM</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025 (2024 Cina) </t>
+          <t>2024 (EV)-2026 (DM)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>5.293 mm – 5.316 mm</t>
+          <t>4.710 mm</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1.988 mm</t>
+          <t>1.810 mm</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.785 mm</t>
+          <t>1.690 mm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>HARUS CUSTOM</t>
+          <t>STANDAR</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalau 17 Durable Premium Pas Sekali | Pernah Coba Xtrem 17 Malah Ketat | </t>
+          <t>Ukuran panjangnya sama jika dibandingkan antara BYD M6 EV (listrik murni) dan varian BYD M6 DM Cross. Keduanya memiliki panjang total 4.710 mm</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1787883311_Foto1_Screenshot 2026-08-28 091244.png</t>
+          <t>1788151668_Foto1_Screenshot 2026-08-31 114709.png</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1787883311_Foto2_Screenshot 2026-08-28 091307.png</t>
+          <t>1788151668_Foto2_Screenshot 2026-08-31 114717.png</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>1787883311_Foto3_Screenshot 2026-08-28 091336.png</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>1787883311_Foto4_Screenshot 2026-08-28 091426.png</t>
-        </is>
-      </c>
+          <t>1788151668_Foto3_Screenshot 2026-08-31 114724.png</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3169,65 +3205,61 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BYD</t>
+          <t>Honda</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>M9</t>
+          <t>Freed</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2012-2015</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>09</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>5.145 mm</t>
+          <t>4.215 mm</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.970 mm</t>
+          <t>1.700 mm</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.805 mm</t>
+          <t>1.740 mm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>HARUS CUSTOM</t>
+          <t>STANDAR</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Sudah Terdaftar Resmi: Hak paten desain industri dan nama BYD M9 telah resmi terdaftar di Pangkalan Data Kekayaan Intelektual (PDKI) Kemenkumham RI sejak pertengahan 2025.</t>
+          <t>Di Indonesia, Honda Freed secara resmi diproduksi dan dipasarkan dari tahun 2009 hingga 2015</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1787967030_Foto1_Screenshot 2026-08-29 082307.png</t>
+          <t>1788153382_Foto1_Screenshot 2026-08-31 120015.png</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1787967030_Foto2_Screenshot 2026-08-29 080638.png</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>1787967030_Foto3_Screenshot 2026-08-29 082318.png</t>
-        </is>
-      </c>
+          <t>1788153382_Foto2_Screenshot 2026-08-31 120009.png</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -3243,32 +3275,32 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>M6 EV / DM</t>
+          <t>Sealion 7</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2024 (EV)-2026 (DM)</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>4.710 mm</t>
+          <t>4.830 mm</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.810 mm</t>
+          <t>1.925 mm</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.690 mm</t>
+          <t>1.620 mm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3276,25 +3308,21 @@
           <t>STANDAR</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Ukuran panjangnya sama jika dibandingkan antara BYD M6 EV (listrik murni) dan varian BYD M6 DM Cross. Keduanya memiliki panjang total 4.710 mm</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1788151668_Foto1_Screenshot 2026-08-31 114709.png</t>
+          <t>1788159040_Foto1_Screenshot 2026-08-31 134837.png</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1788151668_Foto2_Screenshot 2026-08-31 114717.png</t>
+          <t>1788159040_Foto2_Screenshot 2026-08-31 134809.png</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>1788151668_Foto3_Screenshot 2026-08-31 114724.png</t>
+          <t>1788159040_Foto3_Screenshot 2026-08-31 134815.png</t>
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
@@ -3307,17 +3335,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Honda</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Freed</t>
+          <t>Lexus UX 200 Sport</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2012-2015</t>
+          <t>2019-2023</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3327,41 +3355,45 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>4.215 mm</t>
+          <t>4.495 mm</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1.700 mm</t>
+          <t>1.840 mm</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1.740 mm</t>
+          <t>1.520 mm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>STANDAR</t>
+          <t>HARUS CUSTOM</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Di Indonesia, Honda Freed secara resmi diproduksi dan dipasarkan dari tahun 2009 hingga 2015</t>
+          <t>Harus Custom karena spek ukuran diantara no 09 dan 10 ( Bila pakai No 10 kepanjangan dan besar dan bila pakai no 09  juga masih turun ) Info Pak Jamal</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1788153382_Foto1_Screenshot 2026-08-31 120015.png</t>
+          <t>1788321753_Foto1_Screenshot 2026-09-01 180615.png</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1788153382_Foto2_Screenshot 2026-08-31 120009.png</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>1788321753_Foto2_lexus UX 200 1.jpg</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>1788321753_Foto3_Lexus UX 200.jpg</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -3372,131 +3404,66 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BYD</t>
+          <t>BMW</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sealion 7</t>
+          <t>i7 xDrive60</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>08</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>4.830 mm</t>
+          <t>5.391 mm</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.925 mm</t>
+          <t>1.950 mm</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.620 mm</t>
+          <t>1.544 mm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>STANDAR</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+          <t>HARUS CUSTOM</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Kalau No 08 Standar kurang lebar  jadi harus custom (Jamal)</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1788159040_Foto1_Screenshot 2026-08-31 134837.png</t>
+          <t>1788323225_Foto1_Screenshot 2026-09-02 112617.png</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1788159040_Foto2_Screenshot 2026-08-31 134809.png</t>
+          <t>1788323225_Foto2_Screenshot 2026-09-02 112627.png</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1788159040_Foto3_Screenshot 2026-08-31 134815.png</t>
+          <t>1788323225_Foto3_BMW I7 Xdrive 60.jpg</t>
         </is>
       </c>
       <c r="O49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Toyota</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Lexus UX 200 Sport</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2019-2023</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>4.495 mm</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>1.840 mm</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>1.520 mm</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>HARUS CUSTOM</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Harus Custom karena spek ukuran diantara no 09 dan 10 ( Bila pakai No 10 kepanjangan dan besar dan bila pakai no 09  juga masih turun ) Info Pak Jamal</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>1788321753_Foto1_Screenshot 2026-09-01 180615.png</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>1788321753_Foto2_lexus UX 200 1.jpg</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>1788321753_Foto3_Lexus UX 200.jpg</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data_cover.xlsx
+++ b/data_cover.xlsx
@@ -940,13 +940,25 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Karakteristik:Model Pre-facelift (Produksi 2019 – 2022) | Model Facelift / LCI 1 (Produksi 2022 – 2024) | Model Facelift / LCI 2 (Produksi 2024 – Sekarang)</t>
+          <t>Karakteristik:Model Pre | Diedit tgl 2026-09-02 11:40</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1788324039_Foto1_Screenshot 2026-09-02 113346.png</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1788324039_Foto2_Screenshot 2026-09-02 113330.png</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1788324039_Foto3_Screenshot 2026-09-02 113324.png</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">

--- a/data_cover.xlsx
+++ b/data_cover.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cosmic Comp\Documents\GitHub\ukuran-cover-mobil\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A4F145-B4F8-44B9-ACEB-E6616EEF7A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FFC962D-0A9E-4BF5-8800-11CAC186C7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1087,9 +1087,6 @@
     <t>2.030 mm</t>
   </si>
   <si>
-    <t xml:space="preserve">Era Klasik </t>
-  </si>
-  <si>
     <t>1788407727_Foto1_Screenshot 2026-09-03 105429.png</t>
   </si>
   <si>
@@ -1114,9 +1111,6 @@
     <t>1.967 mm</t>
   </si>
   <si>
-    <t>Era Modern</t>
-  </si>
-  <si>
     <t>1788409973_Foto1_Screenshot 2026-09-03 113148.png</t>
   </si>
   <si>
@@ -1124,6 +1118,12 @@
   </si>
   <si>
     <t>1788409973_Foto3_Screenshot 2026-09-03 113158.png</t>
+  </si>
+  <si>
+    <t>Era Klasik  | Kalau Cover Premium Bisa Pakai No 14 | Kalau Durable Pakai 11 (Alternatif)</t>
+  </si>
+  <si>
+    <t>Era Modern  | Kalau Cover Premium Bisa Pakai No 14 | Kalau Durable Pakai 11 (Alternatif)</t>
   </si>
 </sst>
 </file>
@@ -2999,27 +2999,27 @@
         <v>68</v>
       </c>
       <c r="J42" t="s">
+        <v>366</v>
+      </c>
+      <c r="L42" t="s">
         <v>355</v>
       </c>
-      <c r="L42" t="s">
+      <c r="M42" t="s">
         <v>356</v>
       </c>
-      <c r="M42" t="s">
+      <c r="N42" t="s">
         <v>357</v>
-      </c>
-      <c r="N42" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B43" t="s">
         <v>349</v>
       </c>
       <c r="C43" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D43" t="s">
         <v>250</v>
@@ -3028,28 +3028,28 @@
         <v>156</v>
       </c>
       <c r="F43" t="s">
+        <v>360</v>
+      </c>
+      <c r="G43" t="s">
         <v>361</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>362</v>
-      </c>
-      <c r="H43" t="s">
-        <v>363</v>
       </c>
       <c r="I43" t="s">
         <v>68</v>
       </c>
       <c r="J43" t="s">
+        <v>367</v>
+      </c>
+      <c r="L43" t="s">
+        <v>363</v>
+      </c>
+      <c r="M43" t="s">
         <v>364</v>
       </c>
-      <c r="L43" t="s">
+      <c r="N43" t="s">
         <v>365</v>
-      </c>
-      <c r="M43" t="s">
-        <v>366</v>
-      </c>
-      <c r="N43" t="s">
-        <v>367</v>
       </c>
     </row>
   </sheetData>
